--- a/wsad_2026-01_v2.xlsx
+++ b/wsad_2026-01_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.mazur_telemedi\Documents\GitHub\settlement-app2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBA1A8B3-F4A5-4D6F-ACE3-EFE2F967C9CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C2C4EA-FDE1-4877-B310-354C48EC7504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Lekarze_GLOBAL" sheetId="1" r:id="rId1"/>
@@ -1500,7 +1500,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1512,7 +1512,7 @@
       <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1539,10 +1539,10 @@
       <c r="M1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="1" t="s">
         <v>38</v>
       </c>
       <c r="P1" s="1" t="s">

--- a/wsad_2026-01_v2.xlsx
+++ b/wsad_2026-01_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.mazur_telemedi\Documents\GitHub\settlement-app2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C2C4EA-FDE1-4877-B310-354C48EC7504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B05155-5A3E-4C0B-A34E-7F7F2359E7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Lekarze_GLOBAL" sheetId="1" r:id="rId1"/>
@@ -3132,6 +3132,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H141"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="20.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.7265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -6472,6 +6478,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">

--- a/wsad_2026-01_v2.xlsx
+++ b/wsad_2026-01_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.mazur_telemedi\Documents\GitHub\settlement-app2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B05155-5A3E-4C0B-A34E-7F7F2359E7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1914DF20-77BA-40F7-BA70-019524904B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Lekarze_GLOBAL" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,20 @@
     <sheet name="6_Sloty_GLOBAL" sheetId="7" r:id="rId7"/>
     <sheet name="7_Recepty_GLOBAL" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -3133,6 +3146,8 @@
   <dimension ref="A1:H141"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="20.6328125" bestFit="1" customWidth="1"/>
@@ -3158,10 +3173,10 @@
       <c r="F1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6535,6 +6550,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -6596,6 +6615,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -7802,6 +7831,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I93"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="6" max="6" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="20.6328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
